--- a/data/availability/projects/tatweer-misr/fouka-bay.xlsx
+++ b/data/availability/projects/tatweer-misr/fouka-bay.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Fouka Bay latest availability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/tatweer-misr/fouka-bay.xlsx
+++ b/data/availability/projects/tatweer-misr/fouka-bay.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S-CH2</t>
+          <t>S-Ch2</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 BR</t>
+          <t>2 Br</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 BR</t>
+          <t>1 Br</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1 BR</t>
+          <t>1 Br</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S-CH2</t>
+          <t>S-Ch2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CH2</t>
+          <t>Ch2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
